--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Myrhede, Jan Eklund</t>
+          <t>Jan Eklund, Gunnar Myrhede</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Myrhede, Jan Eklund</t>
+          <t>Jan Eklund, Gunnar Myrhede</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Eklund, Gunnar Myrhede</t>
+          <t>Gunnar Myrhede, Jan Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Eklund, Gunnar Myrhede</t>
+          <t>Gunnar Myrhede, Jan Eklund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Myrhede, Jan Eklund</t>
+          <t>Jan Eklund, Gunnar Myrhede</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Eklund, Gunnar Myrhede</t>
+          <t>Gunnar Myrhede, Jan Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128810625</v>
       </c>
       <c r="B2" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128810618</v>
       </c>
       <c r="B3" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44938-2025 artfynd.xlsx
+++ b/artfynd/A 44938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128810625</v>
+        <v>128810618</v>
       </c>
       <c r="B2" t="n">
-        <v>97576</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -780,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128810618</v>
+        <v>128810625</v>
       </c>
       <c r="B3" t="n">
-        <v>92193</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +794,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
